--- a/1109.xlsx
+++ b/1109.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\GC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B4E820-196E-4814-A78F-6DA2D9D955C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2E777D-D146-4DE2-850A-F5C7E1CB8457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4C088012-60FD-4646-BED1-FE274A558489}"/>
   </bookViews>
@@ -744,6 +744,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="30.04.26"/>
@@ -9287,7 +9288,7 @@
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
